--- a/excel_files/9.2.1.xlsx
+++ b/excel_files/9.2.1.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE761352-CED2-44CC-BE12-4BFBC66D490E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15465" windowHeight="12255"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -124,11 +125,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -203,6 +204,11 @@
       <sz val="10"/>
       <name val="Times New Roman Cyr"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial Cyr"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -264,13 +270,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -281,7 +287,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -296,7 +302,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -305,27 +311,34 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Normal_GDP1" xfId="2" xr:uid="{71A112DD-9B94-4901-94C8-8B8284B0F45A}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -341,9 +354,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -381,9 +394,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -418,7 +431,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -453,7 +466,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -626,250 +639,260 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="37.85546875" customWidth="1"/>
     <col min="4" max="19" width="8.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:21" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
-      <c r="T2" s="18"/>
+    <row r="2" spans="1:21" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="18"/>
     </row>
-    <row r="3" spans="1:20" s="2" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:21" s="1" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <v>2007</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="9">
         <v>2008</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="9">
         <v>2009</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="10">
         <v>2010</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="10">
         <v>2011</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="10">
         <v>2012</v>
       </c>
-      <c r="J3" s="11">
+      <c r="J3" s="10">
         <v>2013</v>
       </c>
-      <c r="K3" s="11">
+      <c r="K3" s="10">
         <v>2014</v>
       </c>
-      <c r="L3" s="11">
+      <c r="L3" s="10">
         <v>2015</v>
       </c>
-      <c r="M3" s="11">
+      <c r="M3" s="10">
         <v>2016</v>
       </c>
-      <c r="N3" s="11">
+      <c r="N3" s="10">
         <v>2017</v>
       </c>
-      <c r="O3" s="11">
+      <c r="O3" s="10">
         <v>2018</v>
       </c>
-      <c r="P3" s="11">
+      <c r="P3" s="10">
         <v>2019</v>
       </c>
-      <c r="Q3" s="11">
+      <c r="Q3" s="10">
         <v>2020</v>
       </c>
-      <c r="R3" s="11">
+      <c r="R3" s="10">
         <v>2021</v>
       </c>
-      <c r="S3" s="11">
+      <c r="S3" s="10">
         <v>2022</v>
       </c>
-      <c r="T3" s="11">
+      <c r="T3" s="10">
         <v>2023</v>
       </c>
+      <c r="U3" s="19">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="4" spans="1:20" s="2" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:21" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <v>9.9</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <v>13.2</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="11">
         <v>14.2</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>16.899999999999999</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <v>18.3</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="12">
         <v>12.1</v>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="12">
         <v>15.8</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="12">
         <v>13.7</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="12">
         <v>14</v>
       </c>
-      <c r="M4" s="13">
+      <c r="M4" s="12">
         <v>15.4</v>
       </c>
-      <c r="N4" s="13">
+      <c r="N4" s="12">
         <v>15</v>
       </c>
-      <c r="O4" s="13">
+      <c r="O4" s="12">
         <v>14.3</v>
       </c>
-      <c r="P4" s="13">
+      <c r="P4" s="12">
         <v>13.7</v>
       </c>
-      <c r="Q4" s="16">
+      <c r="Q4" s="12">
         <v>13.1</v>
       </c>
-      <c r="R4" s="16">
+      <c r="R4" s="12">
         <v>11.8</v>
       </c>
-      <c r="S4" s="16">
+      <c r="S4" s="12">
         <v>13.6</v>
       </c>
-      <c r="T4" s="16">
+      <c r="T4" s="12">
         <v>12.6</v>
       </c>
+      <c r="U4" s="20">
+        <v>12.7</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" s="1" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:21" s="1" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <v>2.8</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="13">
         <v>4.9000000000000004</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="13">
         <v>5.6</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="13">
         <v>7.2</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <v>9.9</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="13">
         <v>7</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="13">
         <v>10.3</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="13">
         <v>9.8000000000000007</v>
       </c>
-      <c r="L5" s="14">
+      <c r="L5" s="13">
         <v>10.6</v>
       </c>
-      <c r="M5" s="14">
+      <c r="M5" s="13">
         <v>12.6</v>
       </c>
-      <c r="N5" s="14">
+      <c r="N5" s="13">
         <v>13.4</v>
       </c>
-      <c r="O5" s="14">
+      <c r="O5" s="13">
         <v>13.4</v>
       </c>
-      <c r="P5" s="14">
+      <c r="P5" s="13">
         <v>13.6</v>
       </c>
-      <c r="Q5" s="14">
+      <c r="Q5" s="13">
         <v>12.5</v>
       </c>
-      <c r="R5" s="14">
+      <c r="R5" s="13">
         <v>13.5</v>
       </c>
-      <c r="S5" s="14">
+      <c r="S5" s="13">
         <v>20</v>
       </c>
-      <c r="T5" s="14">
+      <c r="T5" s="13">
         <v>23.6</v>
       </c>
+      <c r="U5" s="21">
+        <v>27.8</v>
+      </c>
     </row>
-    <row r="6" spans="1:20" s="2" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+    <row r="6" spans="1:21" s="1" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="G11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="E13" t="s">
         <v>7</v>
       </c>
